--- a/Assets/Resources/DataFiles/ItemData/ExcelFile/ItemSubStatData.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/ExcelFile/ItemSubStatData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\ItemData\ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3F591C-DD01-40F2-B27B-713DA8B54FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B78185-247A-4FDD-92C8-492E7C09968D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="612" yWindow="1392" windowWidth="23232" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SubStatPools" sheetId="6" r:id="rId1"/>
@@ -21,13 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
-  <si>
-    <t>elementalConfigId</t>
-  </si>
-  <si>
-    <t>memo</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
   <si>
     <t>elementBonusValue</t>
   </si>
@@ -62,9 +56,6 @@
     <t>Utility</t>
   </si>
   <si>
-    <t>ElementalBonusConfigs</t>
-  </si>
-  <si>
     <t>statPoolType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -73,10 +64,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>defencePowerPercent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>critRateFlat</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -140,6 +127,18 @@
   </si>
   <si>
     <t>스킬 범위 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defensePowerPercent</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -498,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.3984375" customWidth="1"/>
@@ -510,47 +509,47 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
         <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -561,13 +560,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -578,16 +577,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -595,16 +594,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
       <c r="D6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -612,16 +611,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -629,13 +628,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D8">
         <v>1.5</v>
@@ -646,16 +645,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -663,16 +662,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -680,16 +679,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D11">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -697,18 +696,35 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D12">
+        <v>15</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13">
         <v>8</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <v>0</v>
       </c>
     </row>
@@ -720,43 +736,44 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="28.5" customWidth="1"/>
-    <col min="2" max="2" width="15.19921875" customWidth="1"/>
-    <col min="3" max="3" width="18.796875" customWidth="1"/>
-    <col min="4" max="4" width="25.3984375" customWidth="1"/>
+    <col min="1" max="1" width="15.19921875" customWidth="1"/>
+    <col min="2" max="2" width="18.796875" customWidth="1"/>
+    <col min="3" max="3" width="25.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
+      <c r="C3">
         <v>0.25</v>
       </c>
     </row>
